--- a/artfynd/A 22390-2026 artfynd.xlsx
+++ b/artfynd/A 22390-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112615422</v>
+        <v>123158010</v>
       </c>
       <c r="B2" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,47 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102110</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Botkyrka, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664018</v>
+        <v>663952</v>
       </c>
       <c r="R2" t="n">
-        <v>6556361</v>
+        <v>6556482</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Räknade till 19 fjäll-/ormvråkar påväg syd/sydväst</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113227306</v>
+        <v>103902285</v>
       </c>
       <c r="B3" t="n">
-        <v>57215</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,26 +810,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Botkyrka, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663952</v>
+        <v>663971</v>
       </c>
       <c r="R3" t="n">
-        <v>6556482</v>
+        <v>6556498</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,27 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Promenad med hunden som nosar under en gran på 3m. På ca 2m höjd motsvarande sida sitter ugglan och blir tyvärr störd av oss och flyger iväg.</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,16 +897,11 @@
         <v>114900375</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1048,52 +1012,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117747946</v>
+        <v>123054279</v>
       </c>
       <c r="B5" t="n">
-        <v>57771</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1102,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>664036</v>
+        <v>664069</v>
       </c>
       <c r="R5" t="n">
-        <v>6556367</v>
+        <v>6556325</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1132,22 +1082,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,11 +1108,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1179,53 +1124,58 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158010</v>
+        <v>112615422</v>
       </c>
       <c r="B6" t="n">
-        <v>57382</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>102110</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Botkyrka, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663952</v>
+        <v>664018</v>
       </c>
       <c r="R6" t="n">
-        <v>6556482</v>
+        <v>6556361</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1199,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Räknade till 19 fjäll-/ormvråkar påväg syd/sydväst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,32 +1246,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123666546</v>
+        <v>113227306</v>
       </c>
       <c r="B7" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1325,9 +1275,10 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1336,13 +1287,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>664163</v>
+        <v>663952</v>
       </c>
       <c r="R7" t="n">
-        <v>6556487</v>
+        <v>6556482</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,22 +1317,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Promenad med hunden som nosar under en gran på 3m. På ca 2m höjd motsvarande sida sitter ugglan och blir tyvärr störd av oss och flyger iväg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1408,43 +1364,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123665825</v>
+        <v>99904752</v>
       </c>
       <c r="B8" t="n">
-        <v>57942</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1453,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>663977</v>
+        <v>663974</v>
       </c>
       <c r="R8" t="n">
-        <v>6556487</v>
+        <v>6556472</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1483,22 +1440,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-04-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-04-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,15 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123665865</v>
+        <v>103902215</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,39 +1493,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Botkyrka, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663977</v>
+        <v>663971</v>
       </c>
       <c r="R9" t="n">
-        <v>6556487</v>
+        <v>6556498</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1600,22 +1552,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,6 +1591,908 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104174109</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>663898</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6556474</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104192277</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>664153</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6556426</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123666546</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>664163</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6556487</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123665825</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>663977</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6556487</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>103710814</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>664164</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6556398</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-09-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-09-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112573488</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>663898</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6556474</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123665865</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>663977</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6556487</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>117747946</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>664036</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6556367</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Peter Nord</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22390-2026 artfynd.xlsx
+++ b/artfynd/A 22390-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123158010</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103902285</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114900375</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123054279</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,6 +1268,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112615422</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113227306</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99904752</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1591,6 +1631,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103902215</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1703,6 +1748,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104174109</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1811,6 +1861,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104192277</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1923,6 +1978,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123666546</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2035,6 +2095,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123665825</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2147,6 +2212,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103710814</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112573488</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2367,6 +2442,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123665865</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2493,8 +2573,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117747946</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>